--- a/data/demo/Megaluz-Traffic-2026-08-12~2026-08-12.xlsx
+++ b/data/demo/Megaluz-Traffic-2026-08-12~2026-08-12.xlsx
@@ -188,7 +188,7 @@
     <t>604903426610284</t>
   </si>
   <si>
-    <t>MEGALUZ Foco LED de 20W-60W, 1800-5700 lm Ultra brillante, luz blanca fría de 6500K, base E27, ahorro energético y alta eficiencia para hogar, tienda y garaje</t>
+    <t>MEGALUZ Foco LED de 20W-60W Ultra brillante, luz blanca fría de 6500K, base E27, ahorro energético y alta eficiencia para hogar, tienda y garaje</t>
   </si>
   <si>
     <t>2929</t>
